--- a/calibration/phase2_bayesian_regression/all_results_summary.xlsx
+++ b/calibration/phase2_bayesian_regression/all_results_summary.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="72">
   <si>
     <t>Group</t>
   </si>
@@ -592,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN17"/>
+  <dimension ref="A1:AN11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:40">
@@ -731,88 +731,88 @@
         <v>48</v>
       </c>
       <c r="F2">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="G2">
-        <v>0.2826086956521739</v>
+        <v>0.3063063063063063</v>
       </c>
       <c r="H2">
-        <v>0.2138400226831436</v>
+        <v>0.229565441608429</v>
       </c>
       <c r="I2">
-        <v>0.1784257255057584</v>
+        <v>0.1762965450773679</v>
       </c>
       <c r="J2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="K2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="L2">
-        <v>-0.0547447272669741</v>
+        <v>-0.08039564784471098</v>
       </c>
       <c r="M2">
-        <v>0.1199327851510843</v>
+        <v>0.1703018594735484</v>
       </c>
       <c r="N2">
-        <v>0.6181308599621438</v>
+        <v>0.6508305115715484</v>
       </c>
       <c r="O2">
-        <v>0.5324035706807424</v>
+        <v>0.5324485900131312</v>
       </c>
       <c r="P2">
-        <v>0.1937973546809044</v>
+        <v>0.2095053942353876</v>
       </c>
       <c r="Q2">
-        <v>0.05053284269818881</v>
+        <v>0.09118987828439752</v>
       </c>
       <c r="R2">
-        <v>0.2696865200996399</v>
+        <v>0.2506728172302246</v>
       </c>
       <c r="S2">
-        <v>0.2679985742902251</v>
+        <v>0.3617210681728442</v>
       </c>
       <c r="T2">
-        <v>0.03902108270827356</v>
+        <v>0.04887492557010781</v>
       </c>
       <c r="U2">
-        <v>0.004697040362616948</v>
+        <v>0.009537474935582007</v>
       </c>
       <c r="V2">
-        <v>0.02649071490419639</v>
+        <v>0.03065969620023674</v>
       </c>
       <c r="W2">
-        <v>0.02531123538850211</v>
+        <v>0.04266277331537714</v>
       </c>
       <c r="X2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="Y2">
-        <v>0.2027410207939508</v>
+        <v>0.2124827530232936</v>
       </c>
       <c r="Z2">
-        <v>0.7145817145817146</v>
+        <v>0.6879297173414821</v>
       </c>
       <c r="AA2">
-        <v>0.7145817145817146</v>
+        <v>0.6787624140565317</v>
       </c>
       <c r="AB2">
-        <v>0.5145283365072439</v>
+        <v>0.6110921008022491</v>
       </c>
       <c r="AC2">
-        <v>0.5145283365072439</v>
+        <v>0.6065872034781129</v>
       </c>
       <c r="AD2">
-        <v>0.2373597025871277</v>
+        <v>0.2429322302341461</v>
       </c>
       <c r="AE2">
-        <v>0.177456756417758</v>
+        <v>0.1762560430145861</v>
       </c>
       <c r="AF2">
-        <v>0.1067372262477875</v>
+        <v>0.0840340182185173</v>
       </c>
       <c r="AG2">
-        <v>0.1590102825933285</v>
+        <v>0.1903345445848304</v>
       </c>
       <c r="AH2">
         <v>10</v>
@@ -821,19 +821,19 @@
         <v>10</v>
       </c>
       <c r="AJ2">
-        <v>-0.0354142971773852</v>
+        <v>-0.05326889653106101</v>
       </c>
       <c r="AK2">
-        <v>-0.08572728928140139</v>
+        <v>-0.1183819215584172</v>
       </c>
       <c r="AL2">
-        <v>-0.1432645119827156</v>
+        <v>-0.11831551595099</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.009167303284950412</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>-0.00450489732413617</v>
       </c>
     </row>
     <row r="3" spans="1:40">
@@ -850,88 +850,88 @@
         <v>48</v>
       </c>
       <c r="F3">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="G3">
-        <v>0.3285714285714286</v>
+        <v>0.2767857142857143</v>
       </c>
       <c r="H3">
-        <v>0.2314896732568741</v>
+        <v>0.2404579967260361</v>
       </c>
       <c r="I3">
-        <v>0.2054634690284729</v>
+        <v>0.1954196244478226</v>
       </c>
       <c r="J3">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="K3">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="L3">
-        <v>-0.0493056419599287</v>
+        <v>-0.2012366033179596</v>
       </c>
       <c r="M3">
-        <v>0.06866697665169552</v>
+        <v>0.02375795735822928</v>
       </c>
       <c r="N3">
-        <v>0.6558314734612937</v>
+        <v>0.6747461826264426</v>
       </c>
       <c r="O3">
-        <v>0.6050146442763572</v>
+        <v>0.5958214317762774</v>
       </c>
       <c r="P3">
-        <v>0.175346183351108</v>
+        <v>0.2491937771971736</v>
       </c>
       <c r="Q3">
-        <v>0.09761378318071368</v>
+        <v>0.1266948761684554</v>
       </c>
       <c r="R3">
-        <v>0.2509080767631531</v>
+        <v>0.8092299103736877</v>
       </c>
       <c r="S3">
-        <v>0.4408562779426575</v>
+        <v>0.6223568320274353</v>
       </c>
       <c r="T3">
-        <v>0.03733388232622432</v>
+        <v>0.06883008222882445</v>
       </c>
       <c r="U3">
-        <v>0.01248085187839074</v>
+        <v>0.0265093644906983</v>
       </c>
       <c r="V3">
-        <v>0.02887738477600229</v>
+        <v>0.02614838549055986</v>
       </c>
       <c r="W3">
-        <v>0.02781028808284447</v>
+        <v>0.03135365914383772</v>
       </c>
       <c r="X3">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="Y3">
-        <v>0.2206122448979592</v>
+        <v>0.2001753826530612</v>
       </c>
       <c r="Z3">
-        <v>0.6689407955596669</v>
+        <v>0.6451612903225806</v>
       </c>
       <c r="AA3">
-        <v>0.6689407955596669</v>
+        <v>0.6622859418558343</v>
       </c>
       <c r="AB3">
-        <v>0.530018590458126</v>
+        <v>0.4685118303164616</v>
       </c>
       <c r="AC3">
-        <v>0.530018590458126</v>
+        <v>0.4749938078362895</v>
       </c>
       <c r="AD3">
-        <v>0.2357246726751328</v>
+        <v>0.2402908951044083</v>
       </c>
       <c r="AE3">
-        <v>0.2123580425977707</v>
+        <v>0.2155411541461945</v>
       </c>
       <c r="AF3">
-        <v>0.119200088083744</v>
+        <v>0.09847182780504227</v>
       </c>
       <c r="AG3">
-        <v>0.1662404835224152</v>
+        <v>0.151223286986351</v>
       </c>
       <c r="AH3">
         <v>10</v>
@@ -940,19 +940,19 @@
         <v>10</v>
       </c>
       <c r="AJ3">
-        <v>-0.02602620422840118</v>
+        <v>-0.0450383722782135</v>
       </c>
       <c r="AK3">
-        <v>-0.05081682918493646</v>
+        <v>-0.07892475085016515</v>
       </c>
       <c r="AL3">
-        <v>-0.07773240017039434</v>
+        <v>-0.1224989010287183</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.01712465153325371</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>0.006481977519827875</v>
       </c>
     </row>
     <row r="4" spans="1:40">
@@ -969,88 +969,88 @@
         <v>49</v>
       </c>
       <c r="F4">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G4">
-        <v>0.2790697674418605</v>
+        <v>0.2972972972972973</v>
       </c>
       <c r="H4">
-        <v>0.1860169619321823</v>
+        <v>0.2042228877544403</v>
       </c>
       <c r="I4">
-        <v>0.182449871075665</v>
+        <v>0.2004245227417432</v>
       </c>
       <c r="J4">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="K4">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="L4">
-        <v>0.07541569190159914</v>
+        <v>0.02244358973486438</v>
       </c>
       <c r="M4">
-        <v>0.09314566769111643</v>
+        <v>0.04062527400892857</v>
       </c>
       <c r="N4">
-        <v>0.5567096655851179</v>
+        <v>0.5970362697637798</v>
       </c>
       <c r="O4">
-        <v>0.5467610151250323</v>
+        <v>0.5884307676532543</v>
       </c>
       <c r="P4">
-        <v>0.07590337877356729</v>
+        <v>0.07068444748182554</v>
       </c>
       <c r="Q4">
-        <v>0.07426636495854848</v>
+        <v>0.0402745396962418</v>
       </c>
       <c r="R4">
-        <v>0.296758234500885</v>
+        <v>0.3361616015434265</v>
       </c>
       <c r="S4">
-        <v>0.4354538335037877</v>
+        <v>0.2107805234547779</v>
       </c>
       <c r="T4">
-        <v>0.009679778761334431</v>
+        <v>0.009240947783103314</v>
       </c>
       <c r="U4">
-        <v>0.01267482438747772</v>
+        <v>0.004562704538070053</v>
       </c>
       <c r="V4">
-        <v>0.02197173236226604</v>
+        <v>0.01192319732860273</v>
       </c>
       <c r="W4">
-        <v>0.03208793515698385</v>
+        <v>0.01376318720137949</v>
       </c>
       <c r="X4">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="Y4">
-        <v>0.2011898323418064</v>
+        <v>0.2089116143170197</v>
       </c>
       <c r="Z4">
-        <v>0.6535618279569891</v>
+        <v>0.6163558663558664</v>
       </c>
       <c r="AA4">
-        <v>0.6535618279569891</v>
+        <v>0.6163558663558664</v>
       </c>
       <c r="AB4">
-        <v>0.4984539981875689</v>
+        <v>0.4359683429388287</v>
       </c>
       <c r="AC4">
-        <v>0.4984539981875689</v>
+        <v>0.4359683429388287</v>
       </c>
       <c r="AD4">
-        <v>0.2115342170000076</v>
+        <v>0.2216529548168182</v>
       </c>
       <c r="AE4">
-        <v>0.189308422139191</v>
+        <v>0.2031148753838732</v>
       </c>
       <c r="AF4">
-        <v>0.09837976843118668</v>
+        <v>0.09460324048995972</v>
       </c>
       <c r="AG4">
-        <v>0.1090878631418163</v>
+        <v>0.07618100278553266</v>
       </c>
       <c r="AH4">
         <v>10</v>
@@ -1059,13 +1059,13 @@
         <v>10</v>
       </c>
       <c r="AJ4">
-        <v>-0.003567090856517269</v>
+        <v>-0.003798365012697119</v>
       </c>
       <c r="AK4">
-        <v>-0.00994865046008564</v>
+        <v>-0.008605502110525465</v>
       </c>
       <c r="AL4">
-        <v>-0.001637013815018809</v>
+        <v>-0.03040990778558374</v>
       </c>
       <c r="AM4">
         <v>0</v>
@@ -1088,88 +1088,88 @@
         <v>49</v>
       </c>
       <c r="F5">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="G5">
-        <v>0.264367816091954</v>
+        <v>0.2410714285714286</v>
       </c>
       <c r="H5">
-        <v>0.1979968398809433</v>
+        <v>0.1886982917785645</v>
       </c>
       <c r="I5">
-        <v>0.187138631939888</v>
+        <v>0.1782374680042267</v>
       </c>
       <c r="J5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="K5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="L5">
-        <v>-0.0180965224584646</v>
+        <v>-0.03138621876702063</v>
       </c>
       <c r="M5">
-        <v>0.03773620573844272</v>
+        <v>0.02579050167973007</v>
       </c>
       <c r="N5">
-        <v>0.5804508230886049</v>
+        <v>0.5616011829219087</v>
       </c>
       <c r="O5">
-        <v>0.5542860796400302</v>
+        <v>0.5339048983958631</v>
       </c>
       <c r="P5">
-        <v>0.1071675423232988</v>
+        <v>0.1112924211525491</v>
       </c>
       <c r="Q5">
-        <v>0.06171478176939078</v>
+        <v>0.05505666376224587</v>
       </c>
       <c r="R5">
-        <v>0.7412256598472595</v>
+        <v>0.2097953355312348</v>
       </c>
       <c r="S5">
-        <v>0.6204698085784912</v>
+        <v>0.687700629234314</v>
       </c>
       <c r="T5">
-        <v>0.01860571378866142</v>
+        <v>0.01592673611900848</v>
       </c>
       <c r="U5">
-        <v>0.01041355831989218</v>
+        <v>0.01319149578569506</v>
       </c>
       <c r="V5">
-        <v>0.01476004095653323</v>
+        <v>0.01041800097698654</v>
       </c>
       <c r="W5">
-        <v>0.0176128986755434</v>
+        <v>0.01687669421525318</v>
       </c>
       <c r="X5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="Y5">
-        <v>0.1944774739067248</v>
+        <v>0.1829559948979592</v>
       </c>
       <c r="Z5">
-        <v>0.6355298913043479</v>
+        <v>0.6191721132897603</v>
       </c>
       <c r="AA5">
-        <v>0.6355298913043479</v>
+        <v>0.6191721132897603</v>
       </c>
       <c r="AB5">
-        <v>0.3779588578131403</v>
+        <v>0.3544473292371924</v>
       </c>
       <c r="AC5">
-        <v>0.3779588578131403</v>
+        <v>0.3544473292371924</v>
       </c>
       <c r="AD5">
-        <v>0.2174346894025803</v>
+        <v>0.2180299758911133</v>
       </c>
       <c r="AE5">
-        <v>0.1829812377691269</v>
+        <v>0.1778344064950943</v>
       </c>
       <c r="AF5">
-        <v>0.1234164834022522</v>
+        <v>0.1008642539381981</v>
       </c>
       <c r="AG5">
-        <v>0.1031615361571312</v>
+        <v>0.1157295554876328</v>
       </c>
       <c r="AH5">
         <v>10</v>
@@ -1178,13 +1178,13 @@
         <v>10</v>
       </c>
       <c r="AJ5">
-        <v>-0.0108582079410553</v>
+        <v>-0.01046082377433777</v>
       </c>
       <c r="AK5">
-        <v>-0.02616474344857467</v>
+        <v>-0.02769628452604567</v>
       </c>
       <c r="AL5">
-        <v>-0.04545276055390806</v>
+        <v>-0.05623575739030327</v>
       </c>
       <c r="AM5">
         <v>0</v>
@@ -1204,91 +1204,91 @@
         <v>46</v>
       </c>
       <c r="E6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F6">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="G6">
-        <v>0.186046511627907</v>
+        <v>0.2072072072072072</v>
       </c>
       <c r="H6">
-        <v>0.1798604875802994</v>
+        <v>0.182037279009819</v>
       </c>
       <c r="I6">
-        <v>0.1514178768149055</v>
+        <v>0.1536805413966391</v>
       </c>
       <c r="J6">
-        <v>0.1514332071389941</v>
+        <v>0.1642723804885967</v>
       </c>
       <c r="K6">
-        <v>0.1514332071389941</v>
+        <v>0.1642723804885967</v>
       </c>
       <c r="L6">
-        <v>-0.1877215769141913</v>
+        <v>-0.1081429420355633</v>
       </c>
       <c r="M6">
-        <v>0.0001012348901420212</v>
+        <v>0.06447729716008377</v>
       </c>
       <c r="N6">
-        <v>0.5453473654473592</v>
+        <v>0.5522574300656523</v>
       </c>
       <c r="O6">
-        <v>0.4803941705700432</v>
+        <v>0.4831473412589758</v>
       </c>
       <c r="P6">
-        <v>0.1473963804716288</v>
+        <v>0.1629421042429434</v>
       </c>
       <c r="Q6">
-        <v>3.314081304325867E-05</v>
+        <v>0.01529217963729989</v>
       </c>
       <c r="R6">
-        <v>0.6024927496910095</v>
+        <v>0.2224995869657268</v>
       </c>
       <c r="S6">
-        <v>3.314081304325867E-05</v>
+        <v>0.4001629183324106</v>
       </c>
       <c r="T6">
-        <v>0.03976028699846644</v>
+        <v>0.02843159650397472</v>
       </c>
       <c r="U6">
-        <v>1.098313489168224E-09</v>
+        <v>0.002418614043514911</v>
       </c>
       <c r="V6">
-        <v>0.01149132527544756</v>
+        <v>0.01150468682186103</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>0.01183213536542475</v>
       </c>
       <c r="X6">
-        <v>0.1514332071389941</v>
+        <v>0.1642723804885967</v>
       </c>
       <c r="Y6">
-        <v>0.1514332071389941</v>
+        <v>0.1642723804885967</v>
       </c>
       <c r="Z6">
-        <v>0.4883928571428572</v>
+        <v>0.6314229249011858</v>
       </c>
       <c r="AA6">
-        <v>0.4883928571428572</v>
+        <v>0.6457509881422925</v>
       </c>
       <c r="AB6">
-        <v>0.2368373960711168</v>
+        <v>0.3885080504653821</v>
       </c>
       <c r="AC6">
-        <v>0.2368373960711168</v>
+        <v>0.3921651403426603</v>
       </c>
       <c r="AD6">
-        <v>0.2081525027751923</v>
+        <v>0.22571662068367</v>
       </c>
       <c r="AE6">
-        <v>0.151404416104389</v>
+        <v>0.1533728656577426</v>
       </c>
       <c r="AF6">
-        <v>0.1017672792077065</v>
+        <v>0.08366741240024567</v>
       </c>
       <c r="AG6">
-        <v>0.002824993551611581</v>
+        <v>0.1044125530703763</v>
       </c>
       <c r="AH6">
         <v>10</v>
@@ -1297,19 +1297,19 @@
         <v>10</v>
       </c>
       <c r="AJ6">
-        <v>-0.02844261076539389</v>
+        <v>-0.02835673761317992</v>
       </c>
       <c r="AK6">
-        <v>-0.06495319487731599</v>
+        <v>-0.06911008880667652</v>
       </c>
       <c r="AL6">
-        <v>-0.1473632396585855</v>
+        <v>-0.1476499246056435</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.01432806324110669</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.003657089877278197</v>
       </c>
     </row>
     <row r="7" spans="1:40">
@@ -1323,91 +1323,91 @@
         <v>47</v>
       </c>
       <c r="E7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="G7">
-        <v>0.2298850574712644</v>
+        <v>0.2053571428571428</v>
       </c>
       <c r="H7">
-        <v>0.1887704879045486</v>
+        <v>0.1849401742219925</v>
       </c>
       <c r="I7">
-        <v>0.1692626029253006</v>
+        <v>0.1592216044664383</v>
       </c>
       <c r="J7">
-        <v>0.1770379178226979</v>
+        <v>0.1631855867346939</v>
       </c>
       <c r="K7">
-        <v>0.1770379178226979</v>
+        <v>0.1631855867346939</v>
       </c>
       <c r="L7">
-        <v>-0.06627150966382733</v>
+        <v>-0.1333119420814235</v>
       </c>
       <c r="M7">
-        <v>0.04391892422268651</v>
+        <v>0.02429125235612994</v>
       </c>
       <c r="N7">
-        <v>0.5632907745924173</v>
+        <v>0.5581014120604715</v>
       </c>
       <c r="O7">
-        <v>0.5195753954064737</v>
+        <v>0.4963798564145315</v>
       </c>
       <c r="P7">
-        <v>0.1377524738681728</v>
+        <v>0.1782246817435537</v>
       </c>
       <c r="Q7">
-        <v>0.02584437991695843</v>
+        <v>0.05078752791242939</v>
       </c>
       <c r="R7">
-        <v>0.2984046737353007</v>
+        <v>0.3460728526115417</v>
       </c>
       <c r="S7">
-        <v>0.4574229121208191</v>
+        <v>0.6342399716377258</v>
       </c>
       <c r="T7">
-        <v>0.0231287553471751</v>
+        <v>0.03530949443239335</v>
       </c>
       <c r="U7">
-        <v>0.003421097226380759</v>
+        <v>0.00829098160200562</v>
       </c>
       <c r="V7">
-        <v>0.01398637907594219</v>
+        <v>0.01239738683935113</v>
       </c>
       <c r="W7">
-        <v>0.01435003099687999</v>
+        <v>0.01229057293207138</v>
       </c>
       <c r="X7">
-        <v>0.1770379178226979</v>
+        <v>0.1631855867346939</v>
       </c>
       <c r="Y7">
-        <v>0.1770379178226979</v>
+        <v>0.1631855867346939</v>
       </c>
       <c r="Z7">
-        <v>0.6235074626865671</v>
+        <v>0.5981924767953102</v>
       </c>
       <c r="AA7">
-        <v>0.6235074626865671</v>
+        <v>0.6196873473375673</v>
       </c>
       <c r="AB7">
-        <v>0.3861401364000659</v>
+        <v>0.3397146348841327</v>
       </c>
       <c r="AC7">
-        <v>0.3861401364000659</v>
+        <v>0.3443963212886268</v>
       </c>
       <c r="AD7">
-        <v>0.2144492566585541</v>
+        <v>0.222618505358696</v>
       </c>
       <c r="AE7">
-        <v>0.1772233098745346</v>
+        <v>0.1748965531587601</v>
       </c>
       <c r="AF7">
-        <v>0.1283896863460541</v>
+        <v>0.0903911367058754</v>
       </c>
       <c r="AG7">
-        <v>0.08502446115016937</v>
+        <v>0.1005334407091141</v>
       </c>
       <c r="AH7">
         <v>10</v>
@@ -1416,117 +1416,120 @@
         <v>10</v>
       </c>
       <c r="AJ7">
-        <v>-0.01950788497924805</v>
+        <v>-0.0257185697555542</v>
       </c>
       <c r="AK7">
-        <v>-0.04371537918594359</v>
+        <v>-0.06172155564593995</v>
       </c>
       <c r="AL7">
-        <v>-0.1119080939512143</v>
+        <v>-0.1274371538311243</v>
       </c>
       <c r="AM7">
-        <v>0</v>
+        <v>0.02149487054225707</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>0.004681686404494179</v>
       </c>
     </row>
     <row r="8" spans="1:40">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
       </c>
+      <c r="D8">
+        <v>0.85</v>
+      </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F8">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="G8">
-        <v>0.5416666666666666</v>
+        <v>0.3066666666666666</v>
       </c>
       <c r="H8">
-        <v>0.2638965547084808</v>
+        <v>0.2188096046447754</v>
       </c>
       <c r="I8">
-        <v>0.2481725085111417</v>
+        <v>0.2178677320480347</v>
       </c>
       <c r="J8">
-        <v>0.2482638888888889</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="K8">
-        <v>0.2482638888888889</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="L8">
-        <v>-0.06296794064395073</v>
+        <v>-0.02910035629336249</v>
       </c>
       <c r="M8">
-        <v>0.0003680776054710844</v>
+        <v>-0.02467056251688549</v>
       </c>
       <c r="N8">
-        <v>0.7236640970434385</v>
+        <v>0.6277261034058557</v>
       </c>
       <c r="O8">
-        <v>0.6894850324141245</v>
+        <v>0.6257207177942258</v>
       </c>
       <c r="P8">
-        <v>0.1137362892429034</v>
+        <v>0.1778405231237412</v>
       </c>
       <c r="Q8">
-        <v>3.051510019780324E-06</v>
+        <v>0.1467480713129044</v>
       </c>
       <c r="R8">
-        <v>0.392626533905665</v>
+        <v>0.8116207122802734</v>
       </c>
       <c r="S8">
-        <v>3.051510019780324E-06</v>
+        <v>0.8479128479957581</v>
       </c>
       <c r="T8">
-        <v>0.03381729598445649</v>
+        <v>0.05556544672773676</v>
       </c>
       <c r="U8">
-        <v>9.31171340081971E-12</v>
+        <v>0.04132887559103083</v>
       </c>
       <c r="V8">
-        <v>0.01827050264550265</v>
+        <v>0.04597948010121923</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>0.03457748917748917</v>
       </c>
       <c r="X8">
-        <v>0.2482638888888889</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="Y8">
-        <v>0.2482638888888889</v>
+        <v>0.2126222222222222</v>
       </c>
       <c r="Z8">
-        <v>0.5</v>
+        <v>0.6964882943143813</v>
       </c>
       <c r="AA8">
-        <v>0.4999999999999999</v>
+        <v>0.6964882943143813</v>
       </c>
       <c r="AB8">
-        <v>0.6380357204505187</v>
+        <v>0.4333730818769181</v>
       </c>
       <c r="AC8">
-        <v>0.6316154151814124</v>
+        <v>0.4333730818769181</v>
       </c>
       <c r="AD8">
-        <v>0.2403015047311783</v>
+        <v>0.2275120317935944</v>
       </c>
       <c r="AE8">
-        <v>0.2482495677279771</v>
+        <v>0.2208404242992401</v>
       </c>
       <c r="AF8">
-        <v>0.0953453853726387</v>
+        <v>0.1441128849983215</v>
       </c>
       <c r="AG8">
-        <v>0.003817779996505407</v>
+        <v>0.1642004102468491</v>
       </c>
       <c r="AH8">
         <v>10</v>
@@ -1535,117 +1538,117 @@
         <v>10</v>
       </c>
       <c r="AJ8">
-        <v>-0.01572404619733911</v>
+        <v>-0.0009418725967407227</v>
       </c>
       <c r="AK8">
-        <v>-0.03417906462931397</v>
+        <v>-0.002005385611629884</v>
       </c>
       <c r="AL8">
-        <v>-0.1137332377328836</v>
+        <v>-0.03109245181083678</v>
       </c>
       <c r="AM8">
-        <v>-5.551115123125783E-17</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>-0.006420305269106308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:40">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C9" t="s">
         <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F9">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="G9">
-        <v>0.4693877551020408</v>
+        <v>0.3766233766233766</v>
       </c>
       <c r="H9">
-        <v>0.2347790449857712</v>
+        <v>0.2090375274419785</v>
       </c>
       <c r="I9">
-        <v>0.2427908778190613</v>
+        <v>0.2069326490163803</v>
       </c>
       <c r="J9">
-        <v>0.2490628904623073</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="K9">
-        <v>0.2490628904623073</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="L9">
-        <v>0.05735035616916939</v>
+        <v>0.1096382900836996</v>
       </c>
       <c r="M9">
-        <v>0.02518244541209669</v>
+        <v>0.1186036810214665</v>
       </c>
       <c r="N9">
-        <v>0.6621876401811301</v>
+        <v>0.6082948691283141</v>
       </c>
       <c r="O9">
-        <v>0.6785917212825571</v>
+        <v>0.6039984593980894</v>
       </c>
       <c r="P9">
-        <v>0.1004383077426833</v>
+        <v>0.1470172608440573</v>
       </c>
       <c r="Q9">
-        <v>0.08176208880482887</v>
+        <v>0.1482713327005312</v>
       </c>
       <c r="R9">
-        <v>0.7239722609519958</v>
+        <v>0.2823934555053711</v>
       </c>
       <c r="S9">
-        <v>0.4876596927642822</v>
+        <v>0.2762813462930567</v>
       </c>
       <c r="T9">
-        <v>0.02591827603769586</v>
+        <v>0.02523466194299105</v>
       </c>
       <c r="U9">
-        <v>0.01302211326002218</v>
+        <v>0.03023559894189322</v>
       </c>
       <c r="V9">
-        <v>0.03484692382958456</v>
+        <v>0.05614082886810159</v>
       </c>
       <c r="W9">
-        <v>0.01777037345550465</v>
+        <v>0.05537575063931061</v>
       </c>
       <c r="X9">
-        <v>0.2490628904623073</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="Y9">
-        <v>0.2490628904623073</v>
+        <v>0.2347782088041828</v>
       </c>
       <c r="Z9">
-        <v>0.6204013377926422</v>
+        <v>0.7162356321839081</v>
       </c>
       <c r="AA9">
-        <v>0.6204013377926422</v>
+        <v>0.7162356321839081</v>
       </c>
       <c r="AB9">
-        <v>0.6459186972483935</v>
+        <v>0.6434946892394726</v>
       </c>
       <c r="AC9">
-        <v>0.6459186972483935</v>
+        <v>0.6434946892394726</v>
       </c>
       <c r="AD9">
-        <v>0.2408510148525238</v>
+        <v>0.22482830286026</v>
       </c>
       <c r="AE9">
-        <v>0.2454139888286591</v>
+        <v>0.2173525542020798</v>
       </c>
       <c r="AF9">
-        <v>0.09357035160064697</v>
+        <v>0.1504005938768387</v>
       </c>
       <c r="AG9">
-        <v>0.03299400955438614</v>
+        <v>0.1713425815105438</v>
       </c>
       <c r="AH9">
         <v>10</v>
@@ -1654,13 +1657,13 @@
         <v>10</v>
       </c>
       <c r="AJ9">
-        <v>0.0080118328332901</v>
+        <v>-0.002104878425598145</v>
       </c>
       <c r="AK9">
-        <v>0.01640408110142699</v>
+        <v>-0.004296409730224715</v>
       </c>
       <c r="AL9">
-        <v>-0.01867621893785439</v>
+        <v>0.001254071856473915</v>
       </c>
       <c r="AM9">
         <v>0</v>
@@ -1674,7 +1677,7 @@
         <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C10" t="s">
         <v>46</v>
@@ -1683,88 +1686,88 @@
         <v>49</v>
       </c>
       <c r="F10">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="G10">
-        <v>0.3958333333333333</v>
+        <v>0.4266666666666667</v>
       </c>
       <c r="H10">
-        <v>0.222265288233757</v>
+        <v>0.2940920889377594</v>
       </c>
       <c r="I10">
-        <v>0.2008737663627283</v>
+        <v>0.2366443711278126</v>
       </c>
       <c r="J10">
-        <v>0.2391493055555556</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="K10">
-        <v>0.2391493055555556</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="L10">
-        <v>0.07060031925485277</v>
+        <v>-0.2022296513625703</v>
       </c>
       <c r="M10">
-        <v>0.1600487156084828</v>
+        <v>0.0326129450625392</v>
       </c>
       <c r="N10">
-        <v>0.6343382552875306</v>
+        <v>0.7851971505901416</v>
       </c>
       <c r="O10">
-        <v>0.5934325148310672</v>
+        <v>0.6662423931351713</v>
       </c>
       <c r="P10">
-        <v>0.1773733235895633</v>
+        <v>0.2053658982117971</v>
       </c>
       <c r="Q10">
-        <v>0.1454116837647493</v>
+        <v>0.05948356541012931</v>
       </c>
       <c r="R10">
-        <v>0.2755082686742147</v>
+        <v>0.4258496839067211</v>
       </c>
       <c r="S10">
-        <v>0.3609980173363394</v>
+        <v>0.266816853816028</v>
       </c>
       <c r="T10">
-        <v>0.04456353005982202</v>
+        <v>0.07661349583849296</v>
       </c>
       <c r="U10">
-        <v>0.02759738177116663</v>
+        <v>0.007453724884403291</v>
       </c>
       <c r="V10">
-        <v>0.05847719988344988</v>
+        <v>0.02534513457556936</v>
       </c>
       <c r="W10">
-        <v>0.0642936056998557</v>
+        <v>0.01625816824576515</v>
       </c>
       <c r="X10">
-        <v>0.2391493055555556</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="Y10">
-        <v>0.2391493055555556</v>
+        <v>0.2446222222222222</v>
       </c>
       <c r="Z10">
-        <v>0.7568058076225045</v>
+        <v>0.3597383720930233</v>
       </c>
       <c r="AA10">
-        <v>0.7568058076225045</v>
+        <v>0.6402616279069768</v>
       </c>
       <c r="AB10">
-        <v>0.7387522578872581</v>
+        <v>0.4008755684885574</v>
       </c>
       <c r="AC10">
-        <v>0.7387522578872581</v>
+        <v>0.5945702677152118</v>
       </c>
       <c r="AD10">
-        <v>0.2304622381925583</v>
+        <v>0.2355819493532181</v>
       </c>
       <c r="AE10">
-        <v>0.2173017768159769</v>
+        <v>0.2422539496107458</v>
       </c>
       <c r="AF10">
-        <v>0.1378456652164459</v>
+        <v>0.1153477132320404</v>
       </c>
       <c r="AG10">
-        <v>0.1478155464488665</v>
+        <v>0.04869544719534327</v>
       </c>
       <c r="AH10">
         <v>10</v>
@@ -1773,19 +1776,19 @@
         <v>10</v>
       </c>
       <c r="AJ10">
-        <v>-0.02139152187102869</v>
+        <v>-0.05744771780994679</v>
       </c>
       <c r="AK10">
-        <v>-0.04090574045646345</v>
+        <v>-0.1189547574549703</v>
       </c>
       <c r="AL10">
-        <v>-0.03196163982481406</v>
+        <v>-0.1458823328016678</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>0.2805232558139535</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>0.1936946992266544</v>
       </c>
     </row>
     <row r="11" spans="1:40">
@@ -1793,7 +1796,7 @@
         <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
         <v>47</v>
@@ -1802,88 +1805,88 @@
         <v>49</v>
       </c>
       <c r="F11">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="G11">
-        <v>0.36</v>
+        <v>0.4805194805194805</v>
       </c>
       <c r="H11">
-        <v>0.2160574197769165</v>
+        <v>0.2399329841136932</v>
       </c>
       <c r="I11">
-        <v>0.2078319042921066</v>
+        <v>0.2413518130779266</v>
       </c>
       <c r="J11">
-        <v>0.2304</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="K11">
-        <v>0.2304</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="L11">
-        <v>0.06225078221824432</v>
+        <v>0.03880901161480588</v>
       </c>
       <c r="M11">
-        <v>0.09795180428773165</v>
+        <v>0.03312506774390056</v>
       </c>
       <c r="N11">
-        <v>0.6241693094094154</v>
+        <v>0.6726690893080599</v>
       </c>
       <c r="O11">
-        <v>0.6083457256215339</v>
+        <v>0.6759877838332202</v>
       </c>
       <c r="P11">
-        <v>0.1455381333827972</v>
+        <v>0.06946747411381116</v>
       </c>
       <c r="Q11">
-        <v>0.1327848279476166</v>
+        <v>0.064925251069007</v>
       </c>
       <c r="R11">
-        <v>0.2980961799621582</v>
+        <v>0.3897486726442972</v>
       </c>
       <c r="S11">
-        <v>0.2450107203589545</v>
+        <v>0.3848821520805359</v>
       </c>
       <c r="T11">
-        <v>0.02821791806495353</v>
+        <v>0.01321729744330852</v>
       </c>
       <c r="U11">
-        <v>0.0225373573329917</v>
+        <v>0.007703804070528019</v>
       </c>
       <c r="V11">
-        <v>0.04198543417366947</v>
+        <v>0.0223191120058958</v>
       </c>
       <c r="W11">
-        <v>0.04040000000000001</v>
+        <v>0.01523584640467758</v>
       </c>
       <c r="X11">
-        <v>0.2304</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="Y11">
-        <v>0.2304</v>
+        <v>0.2496205093607691</v>
       </c>
       <c r="Z11">
-        <v>0.6822916666666666</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AA11">
-        <v>0.6822916666666666</v>
+        <v>0.6216216216216216</v>
       </c>
       <c r="AB11">
-        <v>0.6683002737093038</v>
+        <v>0.6259235309399658</v>
       </c>
       <c r="AC11">
-        <v>0.6683002737093038</v>
+        <v>0.6259235309399658</v>
       </c>
       <c r="AD11">
-        <v>0.2276153117418289</v>
+        <v>0.2352633029222488</v>
       </c>
       <c r="AE11">
-        <v>0.2189666330814362</v>
+        <v>0.2390951216220856</v>
       </c>
       <c r="AF11">
-        <v>0.1407260745763779</v>
+        <v>0.1201512441039085</v>
       </c>
       <c r="AG11">
-        <v>0.1154211461544037</v>
+        <v>0.07829184085130692</v>
       </c>
       <c r="AH11">
         <v>10</v>
@@ -1892,735 +1895,18 @@
         <v>10</v>
       </c>
       <c r="AJ11">
-        <v>-0.008225515484809875</v>
+        <v>0.001418828964233398</v>
       </c>
       <c r="AK11">
-        <v>-0.01582358378788151</v>
+        <v>0.003318694525160315</v>
       </c>
       <c r="AL11">
-        <v>-0.01275330543518063</v>
+        <v>-0.004542223044804158</v>
       </c>
       <c r="AM11">
         <v>0</v>
       </c>
       <c r="AN11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:40">
-      <c r="A12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12">
-        <v>25</v>
-      </c>
-      <c r="G12">
-        <v>0.44</v>
-      </c>
-      <c r="H12">
-        <v>0.2597514092922211</v>
-      </c>
-      <c r="I12">
-        <v>0.243857997165713</v>
-      </c>
-      <c r="J12">
-        <v>0.2464</v>
-      </c>
-      <c r="K12">
-        <v>0.2464</v>
-      </c>
-      <c r="L12">
-        <v>-0.05418591433531272</v>
-      </c>
-      <c r="M12">
-        <v>0.01031656994434693</v>
-      </c>
-      <c r="N12">
-        <v>0.7362791549697615</v>
-      </c>
-      <c r="O12">
-        <v>0.6809069343580572</v>
-      </c>
-      <c r="P12">
-        <v>0.2301883506774902</v>
-      </c>
-      <c r="Q12">
-        <v>0.03992274790714143</v>
-      </c>
-      <c r="R12">
-        <v>0.545557975769043</v>
-      </c>
-      <c r="S12">
-        <v>0.1248056853096929</v>
-      </c>
-      <c r="T12">
-        <v>0.08091408313164936</v>
-      </c>
-      <c r="U12">
-        <v>0.00298573434417012</v>
-      </c>
-      <c r="V12">
-        <v>0.07116190476190476</v>
-      </c>
-      <c r="W12">
-        <v>0.001136842105263159</v>
-      </c>
-      <c r="X12">
-        <v>0.2464</v>
-      </c>
-      <c r="Y12">
-        <v>0.2464</v>
-      </c>
-      <c r="Z12">
-        <v>0.564935064935065</v>
-      </c>
-      <c r="AA12">
-        <v>0.564935064935065</v>
-      </c>
-      <c r="AB12">
-        <v>0.5371333657429913</v>
-      </c>
-      <c r="AC12">
-        <v>0.5371333657429913</v>
-      </c>
-      <c r="AD12">
-        <v>0.2029158920049667</v>
-      </c>
-      <c r="AE12">
-        <v>0.2447306764596464</v>
-      </c>
-      <c r="AF12">
-        <v>0.1706219762563705</v>
-      </c>
-      <c r="AG12">
-        <v>0.04083521453563729</v>
-      </c>
-      <c r="AH12">
-        <v>10</v>
-      </c>
-      <c r="AI12">
-        <v>10</v>
-      </c>
-      <c r="AJ12">
-        <v>-0.01589341212650811</v>
-      </c>
-      <c r="AK12">
-        <v>-0.05537222061170433</v>
-      </c>
-      <c r="AL12">
-        <v>-0.1902656027703488</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:40">
-      <c r="A13" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E13" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13">
-        <v>25</v>
-      </c>
-      <c r="G13">
-        <v>0.52</v>
-      </c>
-      <c r="H13">
-        <v>0.2042993307113647</v>
-      </c>
-      <c r="I13">
-        <v>0.2042821049690247</v>
-      </c>
-      <c r="J13">
-        <v>0.2496</v>
-      </c>
-      <c r="K13">
-        <v>0.2496</v>
-      </c>
-      <c r="L13">
-        <v>0.1814930660602374</v>
-      </c>
-      <c r="M13">
-        <v>0.181562079451023</v>
-      </c>
-      <c r="N13">
-        <v>0.6060542686534146</v>
-      </c>
-      <c r="O13">
-        <v>0.6223541272232463</v>
-      </c>
-      <c r="P13">
-        <v>0.1742598807811737</v>
-      </c>
-      <c r="Q13">
-        <v>0.2529992525279522</v>
-      </c>
-      <c r="R13">
-        <v>0.4654345512390137</v>
-      </c>
-      <c r="S13">
-        <v>0.4667980074882507</v>
-      </c>
-      <c r="T13">
-        <v>0.05794583834556462</v>
-      </c>
-      <c r="U13">
-        <v>0.08186079409726464</v>
-      </c>
-      <c r="V13">
-        <v>0.1062666666666667</v>
-      </c>
-      <c r="W13">
-        <v>0.1262666666666667</v>
-      </c>
-      <c r="X13">
-        <v>0.2496</v>
-      </c>
-      <c r="Y13">
-        <v>0.2496</v>
-      </c>
-      <c r="Z13">
-        <v>0.7948717948717948</v>
-      </c>
-      <c r="AA13">
-        <v>0.7948717948717948</v>
-      </c>
-      <c r="AB13">
-        <v>0.7564995962593217</v>
-      </c>
-      <c r="AC13">
-        <v>0.7564995962593217</v>
-      </c>
-      <c r="AD13">
-        <v>0.2058347314596176</v>
-      </c>
-      <c r="AE13">
-        <v>0.1841666102409363</v>
-      </c>
-      <c r="AF13">
-        <v>0.2009876817464828</v>
-      </c>
-      <c r="AG13">
-        <v>0.2431780695915222</v>
-      </c>
-      <c r="AH13">
-        <v>10</v>
-      </c>
-      <c r="AI13">
-        <v>10</v>
-      </c>
-      <c r="AJ13">
-        <v>-1.722574234008789E-05</v>
-      </c>
-      <c r="AK13">
-        <v>0.01629985856983174</v>
-      </c>
-      <c r="AL13">
-        <v>0.0787393717467785</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:40">
-      <c r="A14" t="s">
-        <v>41</v>
-      </c>
-      <c r="B14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14">
-        <v>25</v>
-      </c>
-      <c r="G14">
-        <v>0.28</v>
-      </c>
-      <c r="H14">
-        <v>0.1766807734966278</v>
-      </c>
-      <c r="I14">
-        <v>0.1458739743373734</v>
-      </c>
-      <c r="J14">
-        <v>0.2016</v>
-      </c>
-      <c r="K14">
-        <v>0.2016</v>
-      </c>
-      <c r="L14">
-        <v>0.1236072743222827</v>
-      </c>
-      <c r="M14">
-        <v>0.2764187780884256</v>
-      </c>
-      <c r="N14">
-        <v>0.5392092174242317</v>
-      </c>
-      <c r="O14">
-        <v>0.4544991194163566</v>
-      </c>
-      <c r="P14">
-        <v>0.2077295684814453</v>
-      </c>
-      <c r="Q14">
-        <v>0.116337759806154</v>
-      </c>
-      <c r="R14">
-        <v>0.359534740447998</v>
-      </c>
-      <c r="S14">
-        <v>0.4416421762459278</v>
-      </c>
-      <c r="T14">
-        <v>0.05328213381004998</v>
-      </c>
-      <c r="U14">
-        <v>0.0291939588290504</v>
-      </c>
-      <c r="V14">
-        <v>0.0739809523809524</v>
-      </c>
-      <c r="W14">
-        <v>0.08026666666666668</v>
-      </c>
-      <c r="X14">
-        <v>0.2016</v>
-      </c>
-      <c r="Y14">
-        <v>0.2016</v>
-      </c>
-      <c r="Z14">
-        <v>0.873015873015873</v>
-      </c>
-      <c r="AA14">
-        <v>0.873015873015873</v>
-      </c>
-      <c r="AB14">
-        <v>0.7989595838335333</v>
-      </c>
-      <c r="AC14">
-        <v>0.7989595838335333</v>
-      </c>
-      <c r="AD14">
-        <v>0.2305802404880524</v>
-      </c>
-      <c r="AE14">
-        <v>0.1818021010389036</v>
-      </c>
-      <c r="AF14">
-        <v>0.1206163316965103</v>
-      </c>
-      <c r="AG14">
-        <v>0.1406844430022231</v>
-      </c>
-      <c r="AH14">
-        <v>10</v>
-      </c>
-      <c r="AI14">
-        <v>10</v>
-      </c>
-      <c r="AJ14">
-        <v>-0.03080679915925441</v>
-      </c>
-      <c r="AK14">
-        <v>-0.08471009800787505</v>
-      </c>
-      <c r="AL14">
-        <v>-0.0913918086752913</v>
-      </c>
-      <c r="AM14">
-        <v>0</v>
-      </c>
-      <c r="AN14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:40">
-      <c r="A15" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E15" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15">
-        <v>25</v>
-      </c>
-      <c r="G15">
-        <v>0.44</v>
-      </c>
-      <c r="H15">
-        <v>0.2665060460567474</v>
-      </c>
-      <c r="I15">
-        <v>0.2764079570770264</v>
-      </c>
-      <c r="J15">
-        <v>0.2464</v>
-      </c>
-      <c r="K15">
-        <v>0.2464</v>
-      </c>
-      <c r="L15">
-        <v>-0.08159921289264371</v>
-      </c>
-      <c r="M15">
-        <v>-0.121785540085334</v>
-      </c>
-      <c r="N15">
-        <v>0.7331193314341666</v>
-      </c>
-      <c r="O15">
-        <v>0.8056171016274192</v>
-      </c>
-      <c r="P15">
-        <v>0.21577183842659</v>
-      </c>
-      <c r="Q15">
-        <v>0.2248951852321625</v>
-      </c>
-      <c r="R15">
-        <v>0.3496182024478912</v>
-      </c>
-      <c r="S15">
-        <v>0.9168925434350967</v>
-      </c>
-      <c r="T15">
-        <v>0.05508311053529156</v>
-      </c>
-      <c r="U15">
-        <v>0.1063418413642793</v>
-      </c>
-      <c r="V15">
-        <v>0.0384</v>
-      </c>
-      <c r="W15">
-        <v>0.07544761904761906</v>
-      </c>
-      <c r="X15">
-        <v>0.2464</v>
-      </c>
-      <c r="Y15">
-        <v>0.2464</v>
-      </c>
-      <c r="Z15">
-        <v>0.5064935064935066</v>
-      </c>
-      <c r="AA15">
-        <v>0.5064935064935066</v>
-      </c>
-      <c r="AB15">
-        <v>0.5697158723629312</v>
-      </c>
-      <c r="AC15">
-        <v>0.5697158723629312</v>
-      </c>
-      <c r="AD15">
-        <v>0.2300420999526978</v>
-      </c>
-      <c r="AE15">
-        <v>0.1950665712356567</v>
-      </c>
-      <c r="AF15">
-        <v>0.1372237801551819</v>
-      </c>
-      <c r="AG15">
-        <v>0.1642061769962311</v>
-      </c>
-      <c r="AH15">
-        <v>10</v>
-      </c>
-      <c r="AI15">
-        <v>10</v>
-      </c>
-      <c r="AJ15">
-        <v>0.009901911020278931</v>
-      </c>
-      <c r="AK15">
-        <v>0.07249777019325254</v>
-      </c>
-      <c r="AL15">
-        <v>0.009123346805572502</v>
-      </c>
-      <c r="AM15">
-        <v>0</v>
-      </c>
-      <c r="AN15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:40">
-      <c r="A16" t="s">
-        <v>41</v>
-      </c>
-      <c r="B16" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16">
-        <v>1.6</v>
-      </c>
-      <c r="E16" t="s">
-        <v>50</v>
-      </c>
-      <c r="F16">
-        <v>22</v>
-      </c>
-      <c r="G16">
-        <v>0.5</v>
-      </c>
-      <c r="H16">
-        <v>0.2569035291671753</v>
-      </c>
-      <c r="I16">
-        <v>0.251611590385437</v>
-      </c>
-      <c r="J16">
-        <v>0.25</v>
-      </c>
-      <c r="K16">
-        <v>0.25</v>
-      </c>
-      <c r="L16">
-        <v>-0.02761411666870117</v>
-      </c>
-      <c r="M16">
-        <v>-0.006446361541748047</v>
-      </c>
-      <c r="N16">
-        <v>0.7113697510448744</v>
-      </c>
-      <c r="O16">
-        <v>0.6972018472714265</v>
-      </c>
-      <c r="P16">
-        <v>0.1283650540492751</v>
-      </c>
-      <c r="Q16">
-        <v>0.1075546687299555</v>
-      </c>
-      <c r="R16">
-        <v>0.4250945697228113</v>
-      </c>
-      <c r="S16">
-        <v>0.3961584568023682</v>
-      </c>
-      <c r="T16">
-        <v>0.04064715672037236</v>
-      </c>
-      <c r="U16">
-        <v>0.02522188001157277</v>
-      </c>
-      <c r="V16">
-        <v>0.02813852813852813</v>
-      </c>
-      <c r="W16">
-        <v>0.01969696969696969</v>
-      </c>
-      <c r="X16">
-        <v>0.25</v>
-      </c>
-      <c r="Y16">
-        <v>0.25</v>
-      </c>
-      <c r="Z16">
-        <v>0.5619834710743802</v>
-      </c>
-      <c r="AA16">
-        <v>0.5619834710743802</v>
-      </c>
-      <c r="AB16">
-        <v>0.6172258297258297</v>
-      </c>
-      <c r="AC16">
-        <v>0.6172258297258297</v>
-      </c>
-      <c r="AD16">
-        <v>0.2355337291955948</v>
-      </c>
-      <c r="AE16">
-        <v>0.2437772303819656</v>
-      </c>
-      <c r="AF16">
-        <v>0.1161400005221367</v>
-      </c>
-      <c r="AG16">
-        <v>0.07606472074985504</v>
-      </c>
-      <c r="AH16">
-        <v>10</v>
-      </c>
-      <c r="AI16">
-        <v>10</v>
-      </c>
-      <c r="AJ16">
-        <v>-0.005291938781738281</v>
-      </c>
-      <c r="AK16">
-        <v>-0.0141679037734479</v>
-      </c>
-      <c r="AL16">
-        <v>-0.02081038531931963</v>
-      </c>
-      <c r="AM16">
-        <v>0</v>
-      </c>
-      <c r="AN16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:40">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-      <c r="B17" t="s">
-        <v>45</v>
-      </c>
-      <c r="C17" t="s">
-        <v>47</v>
-      </c>
-      <c r="E17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F17">
-        <v>23</v>
-      </c>
-      <c r="G17">
-        <v>0.391304347826087</v>
-      </c>
-      <c r="H17">
-        <v>0.1983901262283325</v>
-      </c>
-      <c r="I17">
-        <v>0.1925484389066696</v>
-      </c>
-      <c r="J17">
-        <v>0.2381852551984877</v>
-      </c>
-      <c r="K17">
-        <v>0.2381852551984877</v>
-      </c>
-      <c r="L17">
-        <v>0.1670763748032708</v>
-      </c>
-      <c r="M17">
-        <v>0.1916021890346967</v>
-      </c>
-      <c r="N17">
-        <v>0.5843864775173472</v>
-      </c>
-      <c r="O17">
-        <v>0.5697011042393206</v>
-      </c>
-      <c r="P17">
-        <v>0.1556329766045446</v>
-      </c>
-      <c r="Q17">
-        <v>0.1951753231494323</v>
-      </c>
-      <c r="R17">
-        <v>0.3906616866588593</v>
-      </c>
-      <c r="S17">
-        <v>0.3819378018379211</v>
-      </c>
-      <c r="T17">
-        <v>0.04249449229655916</v>
-      </c>
-      <c r="U17">
-        <v>0.0527472501814145</v>
-      </c>
-      <c r="V17">
-        <v>0.07417559336273892</v>
-      </c>
-      <c r="W17">
-        <v>0.09325771896660363</v>
-      </c>
-      <c r="X17">
-        <v>0.2381852551984877</v>
-      </c>
-      <c r="Y17">
-        <v>0.2381852551984877</v>
-      </c>
-      <c r="Z17">
-        <v>0.8174603174603174</v>
-      </c>
-      <c r="AA17">
-        <v>0.8174603174603174</v>
-      </c>
-      <c r="AB17">
-        <v>0.7785893119226452</v>
-      </c>
-      <c r="AC17">
-        <v>0.7785893119226452</v>
-      </c>
-      <c r="AD17">
-        <v>0.2338529825210571</v>
-      </c>
-      <c r="AE17">
-        <v>0.2274553924798965</v>
-      </c>
-      <c r="AF17">
-        <v>0.1239850074052811</v>
-      </c>
-      <c r="AG17">
-        <v>0.1466438174247742</v>
-      </c>
-      <c r="AH17">
-        <v>10</v>
-      </c>
-      <c r="AI17">
-        <v>10</v>
-      </c>
-      <c r="AJ17">
-        <v>-0.005841687321662903</v>
-      </c>
-      <c r="AK17">
-        <v>-0.01468537327802655</v>
-      </c>
-      <c r="AL17">
-        <v>0.03954234654488764</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
         <v>0</v>
       </c>
     </row>
@@ -2631,7 +1917,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -2713,52 +1999,52 @@
         <v>50</v>
       </c>
       <c r="E2">
-        <v>0.2252845525741577</v>
+        <v>0.2400833904743195</v>
       </c>
       <c r="F2">
-        <v>0.01265193340188617</v>
+        <v>0.01206454748063719</v>
       </c>
       <c r="G2">
-        <v>0.6425849532206188</v>
+        <v>0.6728933973621987</v>
       </c>
       <c r="H2">
-        <v>0.02726052631512155</v>
+        <v>0.02421764668096079</v>
       </c>
       <c r="I2">
-        <v>0.1165255443133709</v>
+        <v>0.1596714316747244</v>
       </c>
       <c r="J2">
-        <v>0.01714815557680745</v>
+        <v>0.03072298828514705</v>
       </c>
       <c r="K2">
-        <v>0.2252572526538524</v>
+        <v>0.2400853042507311</v>
       </c>
       <c r="L2">
-        <v>0.6425270463507814</v>
+        <v>0.6728996359904557</v>
       </c>
       <c r="M2">
-        <v>0.08387616778222415</v>
+        <v>0.09146294774052628</v>
       </c>
       <c r="N2">
-        <v>0.671512396892961</v>
+        <v>0.6285087719298246</v>
       </c>
       <c r="O2">
-        <v>0.5951202017617431</v>
+        <v>0.5866749011222685</v>
       </c>
       <c r="P2">
-        <v>0.232203790177298</v>
+        <v>0.2392093512257705</v>
       </c>
       <c r="Q2">
-        <v>0.1306531774184722</v>
+        <v>0.1028748193181863</v>
       </c>
       <c r="R2">
-        <v>0.008954972228118797</v>
+        <v>0.009534372324365501</v>
       </c>
       <c r="S2">
-        <v>0.02224270004064025</v>
+        <v>0.01267719393139828</v>
       </c>
       <c r="T2">
-        <v>0.2402863812869823</v>
+        <v>0.245257987019972</v>
       </c>
       <c r="U2">
         <v>5</v>
@@ -2778,52 +2064,52 @@
         <v>49</v>
       </c>
       <c r="E3">
-        <v>0.2205385059118271</v>
+        <v>0.2325315564870834</v>
       </c>
       <c r="F3">
-        <v>0.01196769342933299</v>
+        <v>0.01207758332137171</v>
       </c>
       <c r="G3">
-        <v>0.6338322695207779</v>
+        <v>0.6582676453848618</v>
       </c>
       <c r="H3">
-        <v>0.0267472220038278</v>
+        <v>0.02495132790625746</v>
       </c>
       <c r="I3">
-        <v>0.103078895864973</v>
+        <v>0.1055438821089855</v>
       </c>
       <c r="J3">
-        <v>0.02671550284860001</v>
+        <v>0.01923202795569773</v>
       </c>
       <c r="K3">
-        <v>0.2205117407473124</v>
+        <v>0.232533005563801</v>
       </c>
       <c r="L3">
-        <v>0.6337742025424526</v>
+        <v>0.6582713945703011</v>
       </c>
       <c r="M3">
-        <v>0.04630083168068758</v>
+        <v>0.02140293747722031</v>
       </c>
       <c r="N3">
-        <v>0.6688911333958589</v>
+        <v>0.6291849415204678</v>
       </c>
       <c r="O3">
-        <v>0.5842087949104394</v>
+        <v>0.5869324590567599</v>
       </c>
       <c r="P3">
-        <v>0.2223117574759511</v>
+        <v>0.2338963112374243</v>
       </c>
       <c r="Q3">
-        <v>0.1338982449416255</v>
+        <v>0.1065097640655751</v>
       </c>
       <c r="R3">
-        <v>0.003803085882230595</v>
+        <v>0.00469383446658438</v>
       </c>
       <c r="S3">
-        <v>0.02476168181252012</v>
+        <v>0.01536324372895459</v>
       </c>
       <c r="T3">
-        <v>0.2402863812869823</v>
+        <v>0.245257987019972</v>
       </c>
       <c r="U3">
         <v>5</v>
@@ -2843,52 +2129,52 @@
         <v>71</v>
       </c>
       <c r="E4">
-        <v>0.2244549095630646</v>
+        <v>0.2387462437152862</v>
       </c>
       <c r="F4">
-        <v>0.01537597680626377</v>
+        <v>0.01366838236290015</v>
       </c>
       <c r="G4">
-        <v>0.6776953036382615</v>
+        <v>0.7545802606395741</v>
       </c>
       <c r="H4">
-        <v>0.07929562778002738</v>
+        <v>0.09990504730250004</v>
       </c>
       <c r="I4">
-        <v>0.0793853041774137</v>
+        <v>0.1146727878979429</v>
       </c>
       <c r="J4">
-        <v>0.009837950214348114</v>
+        <v>0.02896351243888477</v>
       </c>
       <c r="K4">
-        <v>0.2244161181173984</v>
+        <v>0.2387725213621263</v>
       </c>
       <c r="L4">
-        <v>0.7056193344882842</v>
+        <v>0.8248727952135857</v>
       </c>
       <c r="M4">
-        <v>0.05847327074464158</v>
+        <v>0.06204502989431453</v>
       </c>
       <c r="N4">
-        <v>0.6465021763701513</v>
+        <v>0.5952302631578947</v>
       </c>
       <c r="O4">
-        <v>0.5467233699828246</v>
+        <v>0.5375183992497032</v>
       </c>
       <c r="P4">
-        <v>0.2069168441835286</v>
+        <v>0.2190103963886774</v>
       </c>
       <c r="Q4">
-        <v>0.1821119677553244</v>
+        <v>0.1637567582008308</v>
       </c>
       <c r="R4">
-        <v>0.01080756411088322</v>
+        <v>0.01127983399058644</v>
       </c>
       <c r="S4">
-        <v>0.02867465727456968</v>
+        <v>0.02022927778899057</v>
       </c>
       <c r="T4">
-        <v>0.2402863812869823</v>
+        <v>0.245257987019972</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -2908,52 +2194,52 @@
         <v>48</v>
       </c>
       <c r="E5">
-        <v>0.2188283890485763</v>
+        <v>0.2300004661083221</v>
       </c>
       <c r="F5">
-        <v>0.01423309234856757</v>
+        <v>0.01477079269942952</v>
       </c>
       <c r="G5">
-        <v>0.6304602202450214</v>
+        <v>0.6531148505549774</v>
       </c>
       <c r="H5">
-        <v>0.03035313688271063</v>
+        <v>0.03001387058973662</v>
       </c>
       <c r="I5">
-        <v>0.07916547833796006</v>
+        <v>0.1068732890350578</v>
       </c>
       <c r="J5">
-        <v>0.01677950449284974</v>
+        <v>0.03401361422908341</v>
       </c>
       <c r="K5">
-        <v>0.2187928763355337</v>
+        <v>0.2300124653229832</v>
       </c>
       <c r="L5">
-        <v>0.630380812063432</v>
+        <v>0.6531433595462476</v>
       </c>
       <c r="M5">
-        <v>0.0196598733488757</v>
+        <v>0.03254158446888723</v>
       </c>
       <c r="N5">
-        <v>0.6668229805449342</v>
+        <v>0.6209978070175438</v>
       </c>
       <c r="O5">
-        <v>0.5871501700543578</v>
+        <v>0.5772694284668151</v>
       </c>
       <c r="P5">
-        <v>0.2176340977452558</v>
+        <v>0.2280478779639651</v>
       </c>
       <c r="Q5">
-        <v>0.1510672422432879</v>
+        <v>0.1310378052300159</v>
       </c>
       <c r="R5">
-        <v>0.001363324185290547</v>
+        <v>0.001959053971472906</v>
       </c>
       <c r="S5">
-        <v>0.02074464398295493</v>
+        <v>0.01607801746599244</v>
       </c>
       <c r="T5">
-        <v>0.2402863812869823</v>
+        <v>0.245257987019972</v>
       </c>
       <c r="U5">
         <v>5</v>
@@ -2973,52 +2259,52 @@
         <v>50</v>
       </c>
       <c r="E6">
-        <v>0.1901197493076325</v>
+        <v>0.1817782998085022</v>
       </c>
       <c r="F6">
-        <v>0.01523142917386192</v>
+        <v>0.01091377793703306</v>
       </c>
       <c r="G6">
-        <v>0.5640450666941362</v>
+        <v>0.5471845098868348</v>
       </c>
       <c r="H6">
-        <v>0.03258726887427833</v>
+        <v>0.02642302017162119</v>
       </c>
       <c r="I6">
-        <v>0.1478451533521193</v>
+        <v>0.1108729278661179</v>
       </c>
       <c r="J6">
-        <v>0.0275911647620674</v>
+        <v>0.0216490901112546</v>
       </c>
       <c r="K6">
-        <v>0.1900990979954761</v>
+        <v>0.1817339393320816</v>
       </c>
       <c r="L6">
-        <v>0.5639871595145772</v>
+        <v>0.5470737666976933</v>
       </c>
       <c r="M6">
-        <v>0.1044444259126674</v>
+        <v>0.09005955497394065</v>
       </c>
       <c r="N6">
-        <v>0.6477398889770024</v>
+        <v>0.7121357012750456</v>
       </c>
       <c r="O6">
-        <v>0.4147065469394384</v>
+        <v>0.4887339680594117</v>
       </c>
       <c r="P6">
-        <v>0.2083603352768323</v>
+        <v>0.211914610158443</v>
       </c>
       <c r="Q6">
-        <v>0.1439906357462865</v>
+        <v>0.1269465856924442</v>
       </c>
       <c r="R6">
-        <v>0.01780500664636625</v>
+        <v>0.009226734183563696</v>
       </c>
       <c r="S6">
-        <v>0.01545801734168939</v>
+        <v>0.02225901336388386</v>
       </c>
       <c r="T6">
-        <v>0.1879816937731996</v>
+        <v>0.1968518053712933</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -3038,52 +2324,52 @@
         <v>49</v>
       </c>
       <c r="E7">
-        <v>0.1782024294137955</v>
+        <v>0.1749412178993225</v>
       </c>
       <c r="F7">
-        <v>0.009790818538543081</v>
+        <v>0.01104216953866804</v>
       </c>
       <c r="G7">
-        <v>0.5379750246192166</v>
+        <v>0.529948580884102</v>
       </c>
       <c r="H7">
-        <v>0.02293145701680692</v>
+        <v>0.03347457015320708</v>
       </c>
       <c r="I7">
-        <v>0.0881485587129226</v>
+        <v>0.1063156907575155</v>
       </c>
       <c r="J7">
-        <v>0.02571630537137962</v>
+        <v>0.03021597073646941</v>
       </c>
       <c r="K7">
-        <v>0.1781855960926576</v>
+        <v>0.174895933999394</v>
       </c>
       <c r="L7">
-        <v>0.5379265189508806</v>
+        <v>0.5298056235077288</v>
       </c>
       <c r="M7">
-        <v>0.02051393077870595</v>
+        <v>0.03461113956918616</v>
       </c>
       <c r="N7">
-        <v>0.6430610626486916</v>
+        <v>0.709084699453552</v>
       </c>
       <c r="O7">
-        <v>0.4012530563953788</v>
+        <v>0.4827824031869612</v>
       </c>
       <c r="P7">
-        <v>0.1786671184118568</v>
+        <v>0.1778300686426543</v>
       </c>
       <c r="Q7">
-        <v>0.09701159102662056</v>
+        <v>0.137992580481647</v>
       </c>
       <c r="R7">
-        <v>0.0006975841540958302</v>
+        <v>0.001584597240472848</v>
       </c>
       <c r="S7">
-        <v>0.01146603993135667</v>
+        <v>0.02397293699281847</v>
       </c>
       <c r="T7">
-        <v>0.1879816937731996</v>
+        <v>0.1968518053712933</v>
       </c>
       <c r="U7">
         <v>5</v>
@@ -3103,52 +2389,52 @@
         <v>71</v>
       </c>
       <c r="E8">
-        <v>0.1838038355112076</v>
+        <v>0.1810035347938538</v>
       </c>
       <c r="F8">
-        <v>0.01321886993374041</v>
+        <v>0.01443304916009571</v>
       </c>
       <c r="G8">
-        <v>0.6064060111916323</v>
+        <v>0.6273936822290229</v>
       </c>
       <c r="H8">
-        <v>0.1006013770845246</v>
+        <v>0.2130913014473748</v>
       </c>
       <c r="I8">
-        <v>0.07752026114135217</v>
+        <v>0.09676251266065732</v>
       </c>
       <c r="J8">
-        <v>0.03285712083247388</v>
+        <v>0.02335645875347352</v>
       </c>
       <c r="K8">
-        <v>0.1837435330579757</v>
+        <v>0.1809395174445678</v>
       </c>
       <c r="L8">
-        <v>0.6515831375603377</v>
+        <v>0.6962527174352735</v>
       </c>
       <c r="M8">
-        <v>0.0437127949821021</v>
+        <v>0.0613937922390783</v>
       </c>
       <c r="N8">
-        <v>0.610943695479778</v>
+        <v>0.6725182149362477</v>
       </c>
       <c r="O8">
-        <v>0.3611595384072539</v>
+        <v>0.4208273558150013</v>
       </c>
       <c r="P8">
-        <v>0.1664233478308643</v>
+        <v>0.1640200909461365</v>
       </c>
       <c r="Q8">
-        <v>0.1430825851985779</v>
+        <v>0.1763172253207415</v>
       </c>
       <c r="R8">
-        <v>0.008107929379630011</v>
+        <v>0.01182286280689471</v>
       </c>
       <c r="S8">
-        <v>0.01248996644271693</v>
+        <v>0.02846907906912555</v>
       </c>
       <c r="T8">
-        <v>0.1879816937731996</v>
+        <v>0.1968518053712933</v>
       </c>
       <c r="U8">
         <v>5</v>
@@ -3168,52 +2454,52 @@
         <v>48</v>
       </c>
       <c r="E9">
-        <v>0.1789972096681595</v>
+        <v>0.175482714176178</v>
       </c>
       <c r="F9">
-        <v>0.01218701291598949</v>
+        <v>0.01206512629112192</v>
       </c>
       <c r="G9">
-        <v>0.5399033458829186</v>
+        <v>0.5322347074301768</v>
       </c>
       <c r="H9">
-        <v>0.02854992880683758</v>
+        <v>0.03650928044121506</v>
       </c>
       <c r="I9">
-        <v>0.09271065686768988</v>
+        <v>0.1090198596096157</v>
       </c>
       <c r="J9">
-        <v>0.02415776706121022</v>
+        <v>0.03381207174329993</v>
       </c>
       <c r="K9">
-        <v>0.1789818468324205</v>
+        <v>0.1754355417465784</v>
       </c>
       <c r="L9">
-        <v>0.5398606201236844</v>
+        <v>0.5320785202321417</v>
       </c>
       <c r="M9">
-        <v>0.02529493653175915</v>
+        <v>0.03266021466540719</v>
       </c>
       <c r="N9">
-        <v>0.6389373513084854</v>
+        <v>0.7062158469945355</v>
       </c>
       <c r="O9">
-        <v>0.3911876393810523</v>
+        <v>0.479880299318154</v>
       </c>
       <c r="P9">
-        <v>0.1760957657517414</v>
+        <v>0.1732013379227567</v>
       </c>
       <c r="Q9">
-        <v>0.1066658578161739</v>
+        <v>0.1534991519138906</v>
       </c>
       <c r="R9">
-        <v>0.001062059038894354</v>
+        <v>0.003157036250601597</v>
       </c>
       <c r="S9">
-        <v>0.01181543702964034</v>
+        <v>0.02475142733064394</v>
       </c>
       <c r="T9">
-        <v>0.1879816937731996</v>
+        <v>0.1968518053712933</v>
       </c>
       <c r="U9">
         <v>5</v>
@@ -3233,52 +2519,52 @@
         <v>50</v>
       </c>
       <c r="E10">
-        <v>0.1903989374637604</v>
+        <v>0.193692210316658</v>
       </c>
       <c r="F10">
-        <v>0.01875724564705761</v>
+        <v>0.01434302132803766</v>
       </c>
       <c r="G10">
-        <v>0.5650718575766867</v>
+        <v>0.5749104086765422</v>
       </c>
       <c r="H10">
-        <v>0.04348303063102638</v>
+        <v>0.03227437260380261</v>
       </c>
       <c r="I10">
-        <v>0.1234497431390336</v>
+        <v>0.1133662782120845</v>
       </c>
       <c r="J10">
-        <v>0.02925598420373936</v>
+        <v>0.02769679523746126</v>
       </c>
       <c r="K10">
-        <v>0.1904931430996414</v>
+        <v>0.1936524705631131</v>
       </c>
       <c r="L10">
-        <v>0.5652844331975216</v>
+        <v>0.5748208908954252</v>
       </c>
       <c r="M10">
-        <v>0.09035401909277706</v>
+        <v>0.08931720591412333</v>
       </c>
       <c r="N10">
-        <v>0.646338619402985</v>
+        <v>0.6551418439716312</v>
       </c>
       <c r="O10">
-        <v>0.4252840553331261</v>
+        <v>0.4802413886469232</v>
       </c>
       <c r="P10">
-        <v>0.2048232454015222</v>
+        <v>0.2173091825149175</v>
       </c>
       <c r="Q10">
-        <v>0.1496269320149065</v>
+        <v>0.113090437045271</v>
       </c>
       <c r="R10">
-        <v>0.01146067455444233</v>
+        <v>0.009015993029821421</v>
       </c>
       <c r="S10">
-        <v>0.01192009099315439</v>
+        <v>0.01822984085744576</v>
       </c>
       <c r="T10">
-        <v>0.19176816088013</v>
+        <v>0.2022302699989243</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -3298,52 +2584,52 @@
         <v>49</v>
       </c>
       <c r="E11">
-        <v>0.1817021727561951</v>
+        <v>0.1894342988729477</v>
       </c>
       <c r="F11">
-        <v>0.01328935599232697</v>
+        <v>0.01322936164682293</v>
       </c>
       <c r="G11">
-        <v>0.5465405373097392</v>
+        <v>0.5663596862829614</v>
       </c>
       <c r="H11">
-        <v>0.03180208644806448</v>
+        <v>0.03439666477646679</v>
       </c>
       <c r="I11">
-        <v>0.0679952329409563</v>
+        <v>0.1026548015928441</v>
       </c>
       <c r="J11">
-        <v>0.02723618191298593</v>
+        <v>0.04431115853441345</v>
       </c>
       <c r="K11">
-        <v>0.1817753261667978</v>
+        <v>0.1893995575972853</v>
       </c>
       <c r="L11">
-        <v>0.5467091189308692</v>
+        <v>0.5662671080018622</v>
       </c>
       <c r="M11">
-        <v>0.01911830424572051</v>
+        <v>0.04462262501795135</v>
       </c>
       <c r="N11">
-        <v>0.6438121890547264</v>
+        <v>0.6450576241134751</v>
       </c>
       <c r="O11">
-        <v>0.3988768949884169</v>
+        <v>0.459187170894174</v>
       </c>
       <c r="P11">
-        <v>0.1821275869304512</v>
+        <v>0.189846980673448</v>
       </c>
       <c r="Q11">
-        <v>0.09864678076913323</v>
+        <v>0.1082097867872776</v>
       </c>
       <c r="R11">
-        <v>0.0008067896734101839</v>
+        <v>0.002993938042025848</v>
       </c>
       <c r="S11">
-        <v>0.01050839531355557</v>
+        <v>0.01742073293507234</v>
       </c>
       <c r="T11">
-        <v>0.19176816088013</v>
+        <v>0.2022302699989243</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -3363,52 +2649,52 @@
         <v>71</v>
       </c>
       <c r="E12">
-        <v>0.1862153351306915</v>
+        <v>0.1924674242734909</v>
       </c>
       <c r="F12">
-        <v>0.02125530742983294</v>
+        <v>0.02003652295752468</v>
       </c>
       <c r="G12">
-        <v>0.6088037415295547</v>
+        <v>0.6118339162954722</v>
       </c>
       <c r="H12">
-        <v>0.1415550572317187</v>
+        <v>0.1134150470655263</v>
       </c>
       <c r="I12">
-        <v>0.08686467287850116</v>
+        <v>0.101055305980538</v>
       </c>
       <c r="J12">
-        <v>0.02830150401098611</v>
+        <v>0.04129647761240307</v>
       </c>
       <c r="K12">
-        <v>0.186308241150484</v>
+        <v>0.1924013110535596</v>
       </c>
       <c r="L12">
-        <v>0.6543578684467288</v>
+        <v>0.6467889127915434</v>
       </c>
       <c r="M12">
-        <v>0.06208272489743877</v>
+        <v>0.06499032352765995</v>
       </c>
       <c r="N12">
-        <v>0.6156327736318408</v>
+        <v>0.6094636524822695</v>
       </c>
       <c r="O12">
-        <v>0.3734377662058677</v>
+        <v>0.4238176611408143</v>
       </c>
       <c r="P12">
-        <v>0.1724712125255921</v>
+        <v>0.1777077270058569</v>
       </c>
       <c r="Q12">
-        <v>0.1412932749505245</v>
+        <v>0.1534039235608936</v>
       </c>
       <c r="R12">
-        <v>0.01215479921157844</v>
+        <v>0.008629673764283584</v>
       </c>
       <c r="S12">
-        <v>0.01846078524717297</v>
+        <v>0.02093306168291827</v>
       </c>
       <c r="T12">
-        <v>0.19176816088013</v>
+        <v>0.2022302699989243</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -3428,52 +2714,52 @@
         <v>48</v>
       </c>
       <c r="E13">
-        <v>0.1827046543359757</v>
+        <v>0.18734310567379</v>
       </c>
       <c r="F13">
-        <v>0.01490221433558109</v>
+        <v>0.01673792123776385</v>
       </c>
       <c r="G13">
-        <v>0.5483420868504287</v>
+        <v>0.5608979172967703</v>
       </c>
       <c r="H13">
-        <v>0.03465526302553888</v>
+        <v>0.03939223630489452</v>
       </c>
       <c r="I13">
-        <v>0.0879789383320607</v>
+        <v>0.0897395214900772</v>
       </c>
       <c r="J13">
-        <v>0.01710285253918865</v>
+        <v>0.02496373672353291</v>
       </c>
       <c r="K13">
-        <v>0.182782493012904</v>
+        <v>0.1872951537324829</v>
       </c>
       <c r="L13">
-        <v>0.5485214054295066</v>
+        <v>0.5607862198961487</v>
       </c>
       <c r="M13">
-        <v>0.01395520815287777</v>
+        <v>0.03061723695722168</v>
       </c>
       <c r="N13">
-        <v>0.6417910447761195</v>
+        <v>0.6329122340425533</v>
       </c>
       <c r="O13">
-        <v>0.3970152655663672</v>
+        <v>0.4684098235320932</v>
       </c>
       <c r="P13">
-        <v>0.1793770617797432</v>
+        <v>0.1837891375546852</v>
       </c>
       <c r="Q13">
-        <v>0.1083804617798098</v>
+        <v>0.1333321281518327</v>
       </c>
       <c r="R13">
-        <v>0.001885184979546813</v>
+        <v>0.001788268170542447</v>
       </c>
       <c r="S13">
-        <v>0.01189547087230485</v>
+        <v>0.01592998603233558</v>
       </c>
       <c r="T13">
-        <v>0.19176816088013</v>
+        <v>0.2022302699989243</v>
       </c>
       <c r="U13">
         <v>5</v>
@@ -3481,10 +2767,10 @@
     </row>
     <row r="14" spans="1:21">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
         <v>70</v>
@@ -3493,52 +2779,52 @@
         <v>50</v>
       </c>
       <c r="E14">
-        <v>0.2403622269630432</v>
+        <v>0.2072085529565811</v>
       </c>
       <c r="F14">
-        <v>0.01934802021203703</v>
+        <v>0.01820299765171251</v>
       </c>
       <c r="G14">
-        <v>0.6740997068081451</v>
+        <v>0.6036149690082986</v>
       </c>
       <c r="H14">
-        <v>0.03995684391010823</v>
+        <v>0.04160876555881842</v>
       </c>
       <c r="I14">
-        <v>0.1190533553731853</v>
+        <v>0.1509555473175026</v>
       </c>
       <c r="J14">
-        <v>0.04260336851192487</v>
+        <v>0.02459378418349488</v>
       </c>
       <c r="K14">
-        <v>0.2403622232530851</v>
+        <v>0.2071687475747858</v>
       </c>
       <c r="L14">
-        <v>0.6740997070904698</v>
+        <v>0.6035087928587731</v>
       </c>
       <c r="M14">
-        <v>0.06718182296588503</v>
+        <v>0.09485462944675647</v>
       </c>
       <c r="N14">
-        <v>0.5772889417360286</v>
+        <v>0.7224062702003878</v>
       </c>
       <c r="O14">
-        <v>0.4942268604591972</v>
+        <v>0.626323073819516</v>
       </c>
       <c r="P14">
-        <v>0.2388866171858234</v>
+        <v>0.2123221916857936</v>
       </c>
       <c r="Q14">
-        <v>0.09723636474811517</v>
+        <v>0.1855700303457266</v>
       </c>
       <c r="R14">
-        <v>0.006458207465271731</v>
+        <v>0.01120751178770293</v>
       </c>
       <c r="S14">
-        <v>0.003858086154491145</v>
+        <v>0.04334442723647867</v>
       </c>
       <c r="T14">
-        <v>0.24</v>
+        <v>0.2401754351918337</v>
       </c>
       <c r="U14">
         <v>5</v>
@@ -3546,10 +2832,10 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C15" t="s">
         <v>70</v>
@@ -3558,52 +2844,52 @@
         <v>49</v>
       </c>
       <c r="E15">
-        <v>0.2378874719142914</v>
+        <v>0.2072472006082535</v>
       </c>
       <c r="F15">
-        <v>0.005089695760126381</v>
+        <v>0.01884889741406904</v>
       </c>
       <c r="G15">
-        <v>0.668660450838567</v>
+        <v>0.605903543445103</v>
       </c>
       <c r="H15">
-        <v>0.01064301260866711</v>
+        <v>0.04962828368002645</v>
       </c>
       <c r="I15">
-        <v>0.07108007320042314</v>
+        <v>0.1188810367083204</v>
       </c>
       <c r="J15">
-        <v>0.04946004540059901</v>
+        <v>0.02981166862914616</v>
       </c>
       <c r="K15">
-        <v>0.2378874807865687</v>
+        <v>0.2071946156367718</v>
       </c>
       <c r="L15">
-        <v>0.6686604458901572</v>
+        <v>0.6057522529492032</v>
       </c>
       <c r="M15">
-        <v>0.04417291016414247</v>
+        <v>0.05946244878719031</v>
       </c>
       <c r="N15">
-        <v>0.5720372572334522</v>
+        <v>0.7192550096961862</v>
       </c>
       <c r="O15">
-        <v>0.4634373207645667</v>
+        <v>0.6247794048246775</v>
       </c>
       <c r="P15">
-        <v>0.2391193200458508</v>
+        <v>0.2084196746656424</v>
       </c>
       <c r="Q15">
-        <v>0.03460353848140756</v>
+        <v>0.1779661191288743</v>
       </c>
       <c r="R15">
-        <v>0.001952914627217401</v>
+        <v>0.004735351772163784</v>
       </c>
       <c r="S15">
-        <v>0.005144596651445967</v>
+        <v>0.03713744868324772</v>
       </c>
       <c r="T15">
-        <v>0.24</v>
+        <v>0.2401754351918337</v>
       </c>
       <c r="U15">
         <v>5</v>
@@ -3620,55 +2906,55 @@
         <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E16">
-        <v>0.2422424018383026</v>
+        <v>0.2144519656896591</v>
       </c>
       <c r="F16">
-        <v>0.02444556324165723</v>
+        <v>0.02969587247969813</v>
       </c>
       <c r="G16">
-        <v>0.6791872277860037</v>
+        <v>0.740594873185233</v>
       </c>
       <c r="H16">
-        <v>0.05176343327342207</v>
+        <v>0.2146973130618867</v>
       </c>
       <c r="I16">
-        <v>0.1880334756497679</v>
+        <v>0.09592768204887082</v>
       </c>
       <c r="J16">
-        <v>0.01382964445512448</v>
+        <v>0.05832472611630138</v>
       </c>
       <c r="K16">
-        <v>0.2422423888476373</v>
+        <v>0.2143731730997691</v>
       </c>
       <c r="L16">
-        <v>0.6791872245556055</v>
+        <v>0.8423247249962732</v>
       </c>
       <c r="M16">
-        <v>0.09998196085979198</v>
+        <v>0.07595167420636866</v>
       </c>
       <c r="N16">
-        <v>0.6276470588235294</v>
+        <v>0.6926308985132514</v>
       </c>
       <c r="O16">
-        <v>0.5277868958376279</v>
+        <v>0.5896640331753944</v>
       </c>
       <c r="P16">
-        <v>0.2358130791484667</v>
+        <v>0.1922897952855731</v>
       </c>
       <c r="Q16">
-        <v>0.1189936551464719</v>
+        <v>0.2185727941841196</v>
       </c>
       <c r="R16">
-        <v>0.01855121624701465</v>
+        <v>0.01144221289651052</v>
       </c>
       <c r="S16">
-        <v>0.01562748428741294</v>
+        <v>0.03610266148075721</v>
       </c>
       <c r="T16">
-        <v>0.2425683709869204</v>
+        <v>0.2401754351918337</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -3685,55 +2971,55 @@
         <v>70</v>
       </c>
       <c r="D17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17">
-        <v>0.2367969661951065</v>
+        <v>0.2106210708618164</v>
       </c>
       <c r="F17">
-        <v>0.01335456738421263</v>
+        <v>0.02235937678757346</v>
       </c>
       <c r="G17">
-        <v>0.6672697594484934</v>
+        <v>0.6215281058978945</v>
       </c>
       <c r="H17">
-        <v>0.02875707993303555</v>
+        <v>0.06651331719922828</v>
       </c>
       <c r="I17">
-        <v>0.1591647339278254</v>
+        <v>0.1279307581635489</v>
       </c>
       <c r="J17">
-        <v>0.05104229825482771</v>
+        <v>0.05348741727405</v>
       </c>
       <c r="K17">
-        <v>0.2367969591846701</v>
+        <v>0.2105339748080368</v>
       </c>
       <c r="L17">
-        <v>0.6672697578705795</v>
+        <v>0.6212283919915874</v>
       </c>
       <c r="M17">
-        <v>0.0871315907815407</v>
+        <v>0.05442446305330369</v>
       </c>
       <c r="N17">
-        <v>0.621764705882353</v>
+        <v>0.7116596638655462</v>
       </c>
       <c r="O17">
-        <v>0.5196934846241286</v>
+        <v>0.6138856108487165</v>
       </c>
       <c r="P17">
-        <v>0.2345283903147693</v>
+        <v>0.2031955633155419</v>
       </c>
       <c r="Q17">
-        <v>0.09142487894037196</v>
+        <v>0.190578464671947</v>
       </c>
       <c r="R17">
-        <v>0.01082624626841825</v>
+        <v>0.009727402695218122</v>
       </c>
       <c r="S17">
-        <v>0.01526952041220769</v>
+        <v>0.03834806321027673</v>
       </c>
       <c r="T17">
-        <v>0.2425683709869204</v>
+        <v>0.2401754351918337</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -3744,61 +3030,61 @@
         <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" t="s">
         <v>70</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="E18">
-        <v>0.2337532132863998</v>
+        <v>0.2286242067813873</v>
       </c>
       <c r="F18">
-        <v>0.02921857162203489</v>
+        <v>0.02264527397887236</v>
       </c>
       <c r="G18">
-        <v>0.7554429888463822</v>
+        <v>0.6488949151454311</v>
       </c>
       <c r="H18">
-        <v>0.2244582534948385</v>
+        <v>0.04671772309801749</v>
       </c>
       <c r="I18">
-        <v>0.1616483840449103</v>
+        <v>0.1585610989297646</v>
       </c>
       <c r="J18">
-        <v>0.03118866762180927</v>
+        <v>0.04388537452472557</v>
       </c>
       <c r="K18">
-        <v>0.2337532219857666</v>
+        <v>0.2286495345597719</v>
       </c>
       <c r="L18">
-        <v>0.8360542704258023</v>
+        <v>0.6489535933561538</v>
       </c>
       <c r="M18">
-        <v>0.093410457208225</v>
+        <v>0.09075851331460842</v>
       </c>
       <c r="N18">
-        <v>0.6188235294117647</v>
+        <v>0.6852114898989899</v>
       </c>
       <c r="O18">
-        <v>0.5103083529162651</v>
+        <v>0.6311550835885178</v>
       </c>
       <c r="P18">
-        <v>0.2116667544377599</v>
+        <v>0.2283572586960761</v>
       </c>
       <c r="Q18">
-        <v>0.1761710706157344</v>
+        <v>0.1456996694720282</v>
       </c>
       <c r="R18">
-        <v>0.01888085563028452</v>
+        <v>0.01307409596759244</v>
       </c>
       <c r="S18">
-        <v>0.03179652303366309</v>
+        <v>0.02977610456325668</v>
       </c>
       <c r="T18">
-        <v>0.2425683709869204</v>
+        <v>0.245919773331522</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -3809,713 +3095,63 @@
         <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C19" t="s">
         <v>70</v>
       </c>
       <c r="D19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E19">
-        <v>0.2441025257110596</v>
+        <v>0.2230960130691528</v>
       </c>
       <c r="F19">
-        <v>0.02191074961430954</v>
+        <v>0.01694140854508606</v>
       </c>
       <c r="G19">
-        <v>0.688853939081324</v>
+        <v>0.6375049744126766</v>
       </c>
       <c r="H19">
-        <v>0.05445171843925077</v>
+        <v>0.03507229123960167</v>
       </c>
       <c r="I19">
-        <v>0.1672621696159757</v>
+        <v>0.1224861561604168</v>
       </c>
       <c r="J19">
-        <v>0.03266428352696501</v>
+        <v>0.06569652753123498</v>
       </c>
       <c r="K19">
-        <v>0.2441025342540885</v>
+        <v>0.2231240216620329</v>
       </c>
       <c r="L19">
-        <v>0.6888539412034663</v>
+        <v>0.6375660190989098</v>
       </c>
       <c r="M19">
-        <v>0.1183595653237968</v>
+        <v>0.05075014609072175</v>
       </c>
       <c r="N19">
-        <v>0.6023529411764705</v>
+        <v>0.6845012626262627</v>
       </c>
       <c r="O19">
-        <v>0.5087514254284699</v>
+        <v>0.6307162502506674</v>
       </c>
       <c r="P19">
-        <v>0.2286605334353468</v>
+        <v>0.2317934189309472</v>
       </c>
       <c r="Q19">
-        <v>0.1189257629555426</v>
+        <v>0.1188514355502583</v>
       </c>
       <c r="R19">
-        <v>0.02550443734204762</v>
+        <v>0.003286174966251523</v>
       </c>
       <c r="S19">
-        <v>0.0254367164084294</v>
+        <v>0.02559478577409086</v>
       </c>
       <c r="T19">
-        <v>0.2425683709869204</v>
+        <v>0.245919773331522</v>
       </c>
       <c r="U19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" t="s">
-        <v>70</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20">
-        <v>0.134364727139473</v>
-      </c>
-      <c r="F20">
-        <v>0.03449212000416885</v>
-      </c>
-      <c r="G20">
-        <v>0.4287539453511716</v>
-      </c>
-      <c r="H20">
-        <v>0.07279595181107724</v>
-      </c>
-      <c r="I20">
-        <v>0.1817583099007606</v>
-      </c>
-      <c r="J20">
-        <v>0.03909722804285058</v>
-      </c>
-      <c r="K20">
-        <v>0.1343647270336577</v>
-      </c>
-      <c r="L20">
-        <v>0.4287539434818078</v>
-      </c>
-      <c r="M20">
-        <v>0.1206164685885112</v>
-      </c>
-      <c r="N20">
-        <v>0.8918128654970761</v>
-      </c>
-      <c r="O20">
-        <v>0.6987739878316037</v>
-      </c>
-      <c r="P20">
-        <v>0.1890922271276684</v>
-      </c>
-      <c r="Q20">
-        <v>0.152214578373986</v>
-      </c>
-      <c r="R20">
-        <v>0.01832615687434078</v>
-      </c>
-      <c r="S20">
-        <v>0.06238941798941799</v>
-      </c>
-      <c r="T20">
-        <v>0.1824</v>
-      </c>
-      <c r="U20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E21">
-        <v>0.1274130314588547</v>
-      </c>
-      <c r="F21">
-        <v>0.05563601273454406</v>
-      </c>
-      <c r="G21">
-        <v>0.3876248664943521</v>
-      </c>
-      <c r="H21">
-        <v>0.1232021179537822</v>
-      </c>
-      <c r="I21">
-        <v>0.1870718867083391</v>
-      </c>
-      <c r="J21">
-        <v>0.04775082940285946</v>
-      </c>
-      <c r="K21">
-        <v>0.1274130275850942</v>
-      </c>
-      <c r="L21">
-        <v>0.3876248649419592</v>
-      </c>
-      <c r="M21">
-        <v>0.09704877628323934</v>
-      </c>
-      <c r="N21">
-        <v>0.8732943469785575</v>
-      </c>
-      <c r="O21">
-        <v>0.5973291815397079</v>
-      </c>
-      <c r="P21">
-        <v>0.1420844716169734</v>
-      </c>
-      <c r="Q21">
-        <v>0.2024363257731266</v>
-      </c>
-      <c r="R21">
-        <v>0.01856858530488202</v>
-      </c>
-      <c r="S21">
-        <v>0.07601904761904762</v>
-      </c>
-      <c r="T21">
-        <v>0.1824</v>
-      </c>
-      <c r="U21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" t="s">
-        <v>41</v>
-      </c>
-      <c r="B22" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D22" t="s">
-        <v>71</v>
-      </c>
-      <c r="E22">
-        <v>0.1383702963590622</v>
-      </c>
-      <c r="F22">
-        <v>0.08394357518718713</v>
-      </c>
-      <c r="G22">
-        <v>0.5675381334362806</v>
-      </c>
-      <c r="H22">
-        <v>0.5881115647124332</v>
-      </c>
-      <c r="I22">
-        <v>0.1444213088356008</v>
-      </c>
-      <c r="J22">
-        <v>0.08900504536366426</v>
-      </c>
-      <c r="K22">
-        <v>0.1383703003561748</v>
-      </c>
-      <c r="L22">
-        <v>0.7233865554118416</v>
-      </c>
-      <c r="M22">
-        <v>0.08545766601917197</v>
-      </c>
-      <c r="N22">
-        <v>0.8391812865497077</v>
-      </c>
-      <c r="O22">
-        <v>0.6291341322061386</v>
-      </c>
-      <c r="P22">
-        <v>0.09081199355608009</v>
-      </c>
-      <c r="Q22">
-        <v>0.3021861531255567</v>
-      </c>
-      <c r="R22">
-        <v>0.02312368874127508</v>
-      </c>
-      <c r="S22">
-        <v>0.06807195767195767</v>
-      </c>
-      <c r="T22">
-        <v>0.1824</v>
-      </c>
-      <c r="U22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23">
-        <v>0.134781776368618</v>
-      </c>
-      <c r="F23">
-        <v>0.07870891670717212</v>
-      </c>
-      <c r="G23">
-        <v>0.4028993968294921</v>
-      </c>
-      <c r="H23">
-        <v>0.227460245018816</v>
-      </c>
-      <c r="I23">
-        <v>0.1846023369332155</v>
-      </c>
-      <c r="J23">
-        <v>0.08795306946059844</v>
-      </c>
-      <c r="K23">
-        <v>0.1347817782059447</v>
-      </c>
-      <c r="L23">
-        <v>0.4028993907855556</v>
-      </c>
-      <c r="M23">
-        <v>0.07778304089907896</v>
-      </c>
-      <c r="N23">
-        <v>0.861598440545809</v>
-      </c>
-      <c r="O23">
-        <v>0.5464332551604357</v>
-      </c>
-      <c r="P23">
-        <v>0.1098060576145306</v>
-      </c>
-      <c r="Q23">
-        <v>0.2666618465783482</v>
-      </c>
-      <c r="R23">
-        <v>0.02373761573072028</v>
-      </c>
-      <c r="S23">
-        <v>0.06952698412698413</v>
-      </c>
-      <c r="T23">
-        <v>0.1824</v>
-      </c>
-      <c r="U23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24">
-        <v>0.194961816072464</v>
-      </c>
-      <c r="F24">
-        <v>0.0363807513903848</v>
-      </c>
-      <c r="G24">
-        <v>0.5766349453426952</v>
-      </c>
-      <c r="H24">
-        <v>0.07685194096004025</v>
-      </c>
-      <c r="I24">
-        <v>0.233411291440328</v>
-      </c>
-      <c r="J24">
-        <v>0.1075617951741543</v>
-      </c>
-      <c r="K24">
-        <v>0.1949618244371568</v>
-      </c>
-      <c r="L24">
-        <v>0.5766349468624155</v>
-      </c>
-      <c r="M24">
-        <v>0.1442516263326009</v>
-      </c>
-      <c r="N24">
-        <v>0.6804511278195488</v>
-      </c>
-      <c r="O24">
-        <v>0.3958419851327536</v>
-      </c>
-      <c r="P24">
-        <v>0.2238943970002974</v>
-      </c>
-      <c r="Q24">
-        <v>0.1183975861231973</v>
-      </c>
-      <c r="R24">
-        <v>0.02305517951366242</v>
-      </c>
-      <c r="S24">
-        <v>0.0117010101010101</v>
-      </c>
-      <c r="T24">
-        <v>0.1891555555555555</v>
-      </c>
-      <c r="U24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" t="s">
-        <v>41</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
-      </c>
-      <c r="D25" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25">
-        <v>0.1855598866939545</v>
-      </c>
-      <c r="F25">
-        <v>0.03744658147607609</v>
-      </c>
-      <c r="G25">
-        <v>0.5579826876733279</v>
-      </c>
-      <c r="H25">
-        <v>0.09843632626207702</v>
-      </c>
-      <c r="I25">
-        <v>0.1962106968959172</v>
-      </c>
-      <c r="J25">
-        <v>0.0935707126463947</v>
-      </c>
-      <c r="K25">
-        <v>0.1855598845037203</v>
-      </c>
-      <c r="L25">
-        <v>0.5579826855319793</v>
-      </c>
-      <c r="M25">
-        <v>0.07782618820667267</v>
-      </c>
-      <c r="N25">
-        <v>0.6306390977443609</v>
-      </c>
-      <c r="O25">
-        <v>0.3342555688493469</v>
-      </c>
-      <c r="P25">
-        <v>0.1819634391911446</v>
-      </c>
-      <c r="Q25">
-        <v>0.08162552192583331</v>
-      </c>
-      <c r="R25">
-        <v>0.01380818497180654</v>
-      </c>
-      <c r="S25">
-        <v>0.01622422085951497</v>
-      </c>
-      <c r="T25">
-        <v>0.1891555555555555</v>
-      </c>
-      <c r="U25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:21">
-      <c r="A26" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26">
-        <v>0.2084591090679169</v>
-      </c>
-      <c r="F26">
-        <v>0.0883143744580914</v>
-      </c>
-      <c r="G26">
-        <v>0.7863256058563108</v>
-      </c>
-      <c r="H26">
-        <v>0.6010395884470923</v>
-      </c>
-      <c r="I26">
-        <v>0.1576921000579993</v>
-      </c>
-      <c r="J26">
-        <v>0.1763268810613724</v>
-      </c>
-      <c r="K26">
-        <v>0.20845910219627</v>
-      </c>
-      <c r="L26">
-        <v>0.9421740805824059</v>
-      </c>
-      <c r="M26">
-        <v>0.09255090385668764</v>
-      </c>
-      <c r="N26">
-        <v>0.5634398496240602</v>
-      </c>
-      <c r="O26">
-        <v>0.2868707705722068</v>
-      </c>
-      <c r="P26">
-        <v>0.1629282170705661</v>
-      </c>
-      <c r="Q26">
-        <v>0.1640640690519271</v>
-      </c>
-      <c r="R26">
-        <v>0.02718643878903294</v>
-      </c>
-      <c r="S26">
-        <v>0.007988888888888887</v>
-      </c>
-      <c r="T26">
-        <v>0.1891555555555555</v>
-      </c>
-      <c r="U26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:21">
-      <c r="A27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" t="s">
-        <v>44</v>
-      </c>
-      <c r="C27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D27" t="s">
-        <v>48</v>
-      </c>
-      <c r="E27">
-        <v>0.1923676878213882</v>
-      </c>
-      <c r="F27">
-        <v>0.06216433370786902</v>
-      </c>
-      <c r="G27">
-        <v>0.6197453225521518</v>
-      </c>
-      <c r="H27">
-        <v>0.2632144635610246</v>
-      </c>
-      <c r="I27">
-        <v>0.1967786275347074</v>
-      </c>
-      <c r="J27">
-        <v>0.1306461193103814</v>
-      </c>
-      <c r="K27">
-        <v>0.1923676827595634</v>
-      </c>
-      <c r="L27">
-        <v>0.6197453227479519</v>
-      </c>
-      <c r="M27">
-        <v>0.1202783674298553</v>
-      </c>
-      <c r="N27">
-        <v>0.6231203007518796</v>
-      </c>
-      <c r="O27">
-        <v>0.3286394631439539</v>
-      </c>
-      <c r="P27">
-        <v>0.1736517163178741</v>
-      </c>
-      <c r="Q27">
-        <v>0.1229262376284713</v>
-      </c>
-      <c r="R27">
-        <v>0.02763665978762189</v>
-      </c>
-      <c r="S27">
-        <v>0.02704039586144849</v>
-      </c>
-      <c r="T27">
-        <v>0.1891555555555555</v>
-      </c>
-      <c r="U27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:21">
-      <c r="A28" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" t="s">
-        <v>45</v>
-      </c>
-      <c r="C28" t="s">
-        <v>70</v>
-      </c>
-      <c r="D28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28">
-        <v>0.2120247781276703</v>
-      </c>
-      <c r="F28">
-        <v>0.02731870837315405</v>
-      </c>
-      <c r="G28">
-        <v>0.612596984932666</v>
-      </c>
-      <c r="H28">
-        <v>0.0603814833418963</v>
-      </c>
-      <c r="I28">
-        <v>0.2278130717002428</v>
-      </c>
-      <c r="J28">
-        <v>0.05970518653646054</v>
-      </c>
-      <c r="K28">
-        <v>0.2125189875396899</v>
-      </c>
-      <c r="L28">
-        <v>0.6136905150356503</v>
-      </c>
-      <c r="M28">
-        <v>0.122829495081261</v>
-      </c>
-      <c r="N28">
-        <v>0.75</v>
-      </c>
-      <c r="O28">
-        <v>0.6554213830130203</v>
-      </c>
-      <c r="P28">
-        <v>0.2195415548516174</v>
-      </c>
-      <c r="Q28">
-        <v>0.1712533977417472</v>
-      </c>
-      <c r="R28">
-        <v>0.01976910681510285</v>
-      </c>
-      <c r="S28">
-        <v>0.04720156084602509</v>
-      </c>
-      <c r="T28">
-        <v>0.2432613054132323</v>
-      </c>
-      <c r="U28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:21">
-      <c r="A29" t="s">
-        <v>41</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="C29" t="s">
-        <v>70</v>
-      </c>
-      <c r="D29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E29">
-        <v>0.2114630877971649</v>
-      </c>
-      <c r="F29">
-        <v>0.0127501548081441</v>
-      </c>
-      <c r="G29">
-        <v>0.6104412609744359</v>
-      </c>
-      <c r="H29">
-        <v>0.02356729821313379</v>
-      </c>
-      <c r="I29">
-        <v>0.229953016782855</v>
-      </c>
-      <c r="J29">
-        <v>0.05730764046609094</v>
-      </c>
-      <c r="K29">
-        <v>0.211782191023648</v>
-      </c>
-      <c r="L29">
-        <v>0.6110463174118773</v>
-      </c>
-      <c r="M29">
-        <v>0.07064013761370928</v>
-      </c>
-      <c r="N29">
-        <v>0.7298534798534798</v>
-      </c>
-      <c r="O29">
-        <v>0.6327591535390824</v>
-      </c>
-      <c r="P29">
-        <v>0.2314938119794724</v>
-      </c>
-      <c r="Q29">
-        <v>0.1093104711744053</v>
-      </c>
-      <c r="R29">
-        <v>0.01080890944349762</v>
-      </c>
-      <c r="S29">
-        <v>0.03797196265334756</v>
-      </c>
-      <c r="T29">
-        <v>0.2432613054132323</v>
-      </c>
-      <c r="U29">
         <v>5</v>
       </c>
     </row>
